--- a/Exam/gymtrackerpro/lib/schema/__tests__/bbt/utils/e164PhoneRegex-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/schema/__tests__/bbt/utils/e164PhoneRegex-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="117">
-  <si>
-    <t>Statement: e164PhoneRegex – pattern /^\+?[1-9]\d{1,14}$/ validates simplified E.164 phone numbers.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="103">
+  <si>
+    <t>Statement: e164PhoneRegex – Tests whether a string matches the pattern /^\+?[1-9]\d{1,14}$/. Returns true for strings that optionally start with "+", begin with a non-zero digit, and contain between 2 and 15 digits in total (excluding the optional "+"). Returns false for strings that start with "0", contain spaces, dashes, parentheses, or non-digit characters, consist of "+" alone, or are empty.</t>
   </si>
   <si>
     <t/>
@@ -31,25 +31,25 @@
     <t>Data</t>
   </si>
   <si>
-    <t>Input: string s</t>
+    <t>Input: string s passed to e164PhoneRegex.test(s)</t>
   </si>
   <si>
     <t>precondition</t>
   </si>
   <si>
-    <t>None</t>
+    <t>No preconditions. The regex is applied directly to the input string.</t>
   </si>
   <si>
     <t>Results</t>
   </si>
   <si>
-    <t>Output: boolean</t>
+    <t>Output: boolean — true if the string satisfies /^\+?[1-9]\d{1,14}$/, false otherwise.</t>
   </si>
   <si>
     <t>postcondition</t>
   </si>
   <si>
-    <t>True if format matches.</t>
+    <t>Result reflects structural conformance only. Real-world carrier or country-code validity is not checked.</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -64,64 +64,55 @@
     <t>Invalid EC</t>
   </si>
   <si>
-    <t>Plus prefix</t>
-  </si>
-  <si>
-    <t>+40712345678</t>
-  </si>
-  <si>
-    <t>No plus prefix</t>
-  </si>
-  <si>
-    <t>40712345678</t>
-  </si>
-  <si>
-    <t>Starts with 0</t>
-  </si>
-  <si>
-    <t>0712345678</t>
-  </si>
-  <si>
-    <t>Starts with +0</t>
-  </si>
-  <si>
-    <t>+0712345678</t>
-  </si>
-  <si>
-    <t>Spaces</t>
-  </si>
-  <si>
-    <t>+44 20 1234 5678</t>
-  </si>
-  <si>
-    <t>Dashes</t>
-  </si>
-  <si>
-    <t>+1-800-555-5555</t>
-  </si>
-  <si>
-    <t>Parentheses</t>
-  </si>
-  <si>
-    <t>+1(800)5551234</t>
-  </si>
-  <si>
-    <t>Alpha chars</t>
-  </si>
-  <si>
-    <t>ABCDEFG</t>
-  </si>
-  <si>
-    <t>Only plus</t>
-  </si>
-  <si>
-    <t>+</t>
+    <t>Optional "+" prefix</t>
+  </si>
+  <si>
+    <t>"+40712345678" (with + prefix) → true</t>
+  </si>
+  <si>
+    <t>"40712345678" (without + prefix) → true</t>
+  </si>
+  <si>
+    <t>Leading digit</t>
+  </si>
+  <si>
+    <t>"0712345678" (starts with 0) → false</t>
+  </si>
+  <si>
+    <t>Leading digit after "+"</t>
+  </si>
+  <si>
+    <t>"+0712345678" (starts with +0) → false</t>
+  </si>
+  <si>
+    <t>Non-digit characters</t>
+  </si>
+  <si>
+    <t>"+44 20 1234 5678" (contains spaces) → false</t>
+  </si>
+  <si>
+    <t>"+1-800-555-5555" (contains dashes) → false</t>
+  </si>
+  <si>
+    <t>"+1(800)5551234" (contains parentheses) → false</t>
+  </si>
+  <si>
+    <t>Alphabetic input</t>
+  </si>
+  <si>
+    <t>"ABCDEFG" (alphabetic only) → false</t>
+  </si>
+  <si>
+    <t>Bare "+" sign</t>
+  </si>
+  <si>
+    <t>"+" (plus sign only, no digits) → false</t>
   </si>
   <si>
     <t>Empty string</t>
   </si>
   <si>
-    <t>""</t>
+    <t>"" (empty string) → false</t>
   </si>
   <si>
     <t>No TC</t>
@@ -199,76 +190,64 @@
     <t>EC-9</t>
   </si>
   <si>
-    <t>"+"</t>
+    <t>"+" (plus only)</t>
   </si>
   <si>
     <t>EC-10</t>
   </si>
   <si>
+    <t>"" (empty string)</t>
+  </si>
+  <si>
     <t>Number BVA</t>
   </si>
   <si>
     <t>BVA Test Case</t>
   </si>
   <si>
-    <t>Digit count</t>
-  </si>
-  <si>
-    <t>1 digit after + (Below Min)</t>
-  </si>
-  <si>
-    <t>2 digits after + (At Min)</t>
-  </si>
-  <si>
-    <t>3 digits after + (Above Min)</t>
-  </si>
-  <si>
-    <t>14 digits after + (Below Max)</t>
-  </si>
-  <si>
-    <t>15 digits after + (At Max)</t>
-  </si>
-  <si>
-    <t>16 digits after + (Above Max)</t>
+    <t>Total digit count (excl. optional "+")</t>
+  </si>
+  <si>
+    <t>1 digit ("1", min − 1): below minimum → false; 2 digits ("12", min): at minimum → true; 3 digits ("+123", min + 1): above minimum → true; 14 digits ("+12345678901234", max − 1): below maximum → true; 15 digits ("+123456789012345", max): at maximum → true; 16 digits ("+1234567890123456", max + 1): above maximum → false</t>
   </si>
   <si>
     <t>BVA</t>
   </si>
   <si>
-    <t>BVA-1 len 1</t>
-  </si>
-  <si>
-    <t>"1"</t>
-  </si>
-  <si>
-    <t>BVA-1 len 2</t>
-  </si>
-  <si>
-    <t>"12"</t>
-  </si>
-  <si>
-    <t>BVA-1 len 3</t>
-  </si>
-  <si>
-    <t>"+123"</t>
-  </si>
-  <si>
-    <t>BVA-1 len 14</t>
-  </si>
-  <si>
-    <t>"+12345678901234"</t>
-  </si>
-  <si>
-    <t>BVA-1 len 15</t>
-  </si>
-  <si>
-    <t>"+123456789012345"</t>
-  </si>
-  <si>
-    <t>BVA-1 len 16</t>
-  </si>
-  <si>
-    <t>"+1234567890123456"</t>
+    <t>BVA-1 (digits=1)</t>
+  </si>
+  <si>
+    <t>"1" (1 digit, below minimum)</t>
+  </si>
+  <si>
+    <t>BVA-1 (digits=2)</t>
+  </si>
+  <si>
+    <t>"12" (2 digits, at minimum)</t>
+  </si>
+  <si>
+    <t>BVA-1 (digits=3)</t>
+  </si>
+  <si>
+    <t>"+123" (3 digits with +, above minimum)</t>
+  </si>
+  <si>
+    <t>BVA-1 (digits=14)</t>
+  </si>
+  <si>
+    <t>"+12345678901234" (14 digits with +, below maximum)</t>
+  </si>
+  <si>
+    <t>BVA-1 (digits=15)</t>
+  </si>
+  <si>
+    <t>"+123456789012345" (15 digits with +, at maximum)</t>
+  </si>
+  <si>
+    <t>BVA-1 (digits=16)</t>
+  </si>
+  <si>
+    <t>"+1234567890123456" (16 digits with +, above maximum)</t>
   </si>
   <si>
     <t>TC from EC</t>
@@ -277,57 +256,36 @@
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>"+40712345678" (With +)</t>
-  </si>
-  <si>
-    <t>"40712345678" (Without +)</t>
-  </si>
-  <si>
-    <t>"0712345678" (Starts with 0)</t>
-  </si>
-  <si>
-    <t>"+0712345678" (Starts with +0)</t>
-  </si>
-  <si>
-    <t>"+44 20 1234 5678" (Spaces)</t>
-  </si>
-  <si>
-    <t>"+1-800-555-5555" (Dashes)</t>
-  </si>
-  <si>
-    <t>"+1(800)5551234" (Parentheses)</t>
-  </si>
-  <si>
-    <t>"ABCDEFG" (Alpha)</t>
-  </si>
-  <si>
-    <t>"+" (Plus only)</t>
-  </si>
-  <si>
-    <t>"" (Empty)</t>
+    <t>"+40712345678" (with + prefix)</t>
+  </si>
+  <si>
+    <t>"40712345678" (without + prefix)</t>
+  </si>
+  <si>
+    <t>"0712345678" (starts with 0)</t>
+  </si>
+  <si>
+    <t>"+0712345678" (starts with +0)</t>
+  </si>
+  <si>
+    <t>"+44 20 1234 5678" (contains spaces)</t>
+  </si>
+  <si>
+    <t>"+1-800-555-5555" (contains dashes)</t>
+  </si>
+  <si>
+    <t>"+1(800)5551234" (contains parentheses)</t>
+  </si>
+  <si>
+    <t>"ABCDEFG" (alphabetic only)</t>
+  </si>
+  <si>
+    <t>"+" (plus sign only, no digits)</t>
   </si>
   <si>
     <t>BVA-1</t>
   </si>
   <si>
-    <t>1 digit after + (Too short)</t>
-  </si>
-  <si>
-    <t>2 digits after + (Min)</t>
-  </si>
-  <si>
-    <t>3 digits after + (Inside)</t>
-  </si>
-  <si>
-    <t>14 digits after + (Inside)</t>
-  </si>
-  <si>
-    <t>15 digits after + (Max)</t>
-  </si>
-  <si>
-    <t>16 digits after + (Too long)</t>
-  </si>
-  <si>
     <t>Testing</t>
   </si>
   <si>
@@ -358,7 +316,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>UTILS-E164</t>
+    <t>SCHEMA-15</t>
   </si>
   <si>
     <t>n/a</t>
@@ -924,10 +882,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>1</v>
@@ -938,13 +896,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -952,13 +910,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -966,13 +924,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -980,13 +938,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -994,13 +952,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1008,13 +966,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1022,13 +980,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1036,13 +994,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1065,19 +1023,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>36</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1085,16 +1043,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1102,16 +1060,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1119,16 +1077,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1136,16 +1094,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1153,16 +1111,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1170,16 +1128,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1187,16 +1145,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1204,16 +1162,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1221,16 +1179,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1238,16 +1196,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1258,7 +1216,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1268,13 +1226,13 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1282,65 +1240,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -1363,19 +1266,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>38</v>
-      </c>
       <c r="E1" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1383,16 +1286,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1400,16 +1303,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1417,16 +1320,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1434,16 +1337,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1451,16 +1354,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1468,16 +1371,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1501,22 +1404,22 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>38</v>
-      </c>
       <c r="F1" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1524,19 +1427,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1544,19 +1447,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1564,19 +1467,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1584,19 +1487,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1604,19 +1507,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1624,19 +1527,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1644,19 +1547,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1664,19 +1567,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1684,19 +1587,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1704,19 +1607,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>95</v>
+        <v>59</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1727,16 +1630,16 @@
         <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1747,16 +1650,16 @@
         <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1767,16 +1670,16 @@
         <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1787,16 +1690,16 @@
         <v>1</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1807,16 +1710,16 @@
         <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1827,16 +1730,16 @@
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1864,16 +1767,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -1881,39 +1784,39 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="B3" s="1">
         <v>16</v>
@@ -1928,19 +1831,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/Exam/gymtrackerpro/lib/schema/__tests__/bbt/utils/e164PhoneRegex-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/schema/__tests__/bbt/utils/e164PhoneRegex-bbt-form.xlsx
@@ -316,7 +316,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>SCHEMA-15</t>
+    <t>SCHEMA-17</t>
   </si>
   <si>
     <t>n/a</t>

--- a/Exam/gymtrackerpro/lib/schema/__tests__/bbt/utils/e164PhoneRegex-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/schema/__tests__/bbt/utils/e164PhoneRegex-bbt-form.xlsx
@@ -316,7 +316,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>SCHEMA-17</t>
+    <t>SCHEMA-19</t>
   </si>
   <si>
     <t>n/a</t>
